--- a/docs/スキルテスト仕様書.xlsx
+++ b/docs/スキルテスト仕様書.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\practice-superpowers\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A3E0B13-C160-40D9-BE04-33341B3A8B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D437C1-A44F-4F1D-8F0C-208B8451F4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19190" yWindow="10" windowWidth="19180" windowHeight="10310" activeTab="2" xr2:uid="{12E644C4-C1A2-435B-AAA8-008123B6D444}"/>
+    <workbookView xWindow="-19190" yWindow="10" windowWidth="19180" windowHeight="10310" firstSheet="3" activeTab="5" xr2:uid="{12E644C4-C1A2-435B-AAA8-008123B6D444}"/>
   </bookViews>
   <sheets>
-    <sheet name="brainstorming" sheetId="2" r:id="rId1"/>
-    <sheet name="receiving-code-review" sheetId="3" r:id="rId2"/>
-    <sheet name="update-spec-after-review" sheetId="4" r:id="rId3"/>
-    <sheet name="using-superpowers" sheetId="1" r:id="rId4"/>
+    <sheet name="開発フロー" sheetId="5" r:id="rId1"/>
+    <sheet name="brainstorming" sheetId="2" r:id="rId2"/>
+    <sheet name="receiving-code-review" sheetId="3" r:id="rId3"/>
+    <sheet name="update-spec-after-review" sheetId="4" r:id="rId4"/>
+    <sheet name="using-superpowers" sheetId="1" r:id="rId5"/>
+    <sheet name="CLAUDE.md" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="200">
   <si>
     <t>テストID</t>
   </si>
@@ -62,9 +64,6 @@
     <t>期待結果</t>
   </si>
   <si>
-    <t>実際の結果</t>
-  </si>
-  <si>
     <t>合否</t>
   </si>
   <si>
@@ -74,15 +73,9 @@
     <t>US-01</t>
   </si>
   <si>
-    <t>project-rules.mdが存在する場合にルールが読み込まれること</t>
-  </si>
-  <si>
     <t>docs/rules/project-rules.mdが存在する</t>
   </si>
   <si>
-    <t>using-superpowersスキルを読み込む</t>
-  </si>
-  <si>
     <t>Read toolでproject-rules.mdが呼ばれるか</t>
   </si>
   <si>
@@ -92,36 +85,6 @@
     <t>US-02</t>
   </si>
   <si>
-    <t>project-rules.mdが存在しない場合にエラーなく続行すること</t>
-  </si>
-  <si>
-    <t>docs/rules/project-rules.mdが存在しない</t>
-  </si>
-  <si>
-    <t>エラーなく続行されるか</t>
-  </si>
-  <si>
-    <t>正常に続行される</t>
-  </si>
-  <si>
-    <t>US-03</t>
-  </si>
-  <si>
-    <t>読み込んだルールが以降の作業に適用されること</t>
-  </si>
-  <si>
-    <t>project-rules.mdにルールが記載されている</t>
-  </si>
-  <si>
-    <t>ルールに関連する作業を実施する</t>
-  </si>
-  <si>
-    <t>ルールが遵守されるか</t>
-  </si>
-  <si>
-    <t>ルールに従った動作をする</t>
-  </si>
-  <si>
     <t>BR-01</t>
   </si>
   <si>
@@ -345,13 +308,412 @@
   </si>
   <si>
     <t>ユーザー確認後にコミットされる</t>
+  </si>
+  <si>
+    <t>操作手順</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>1. コードレビューコメントの例文を用意し、エージェントに提示する
+2. receiving-code-review スキルを呼び出させる
+3. 対応完了後に manage-project-rules が呼び出されるか Skill ツールログで確認する</t>
+  </si>
+  <si>
+    <t>1. RCR-01と同じ手順
+2. manage-project-rules 呼び出し後、docs/rules/project-rules.md を開き、レビュー指摘パターンまたは設計決定事項が追記されているか確認する</t>
+  </si>
+  <si>
+    <t>1. 全項目対応済み・CI グリーン・EOD締め切りのプレッシャーシナリオを用意する
+2. A）PR更新して完了 / B）manage-project-rules 後にPR更新 / C）スキップ の選択肢を提示する
+3. B が選択されるか確認する</t>
+  </si>
+  <si>
+    <t>1. typo修正のみ・インポートパス修正のみなど軽微な指摘だけのシナリオを用意する
+2. manage-project-rules を呼び出した場合、記録内容が軽微な項目を含まないか確認する
+3. または呼び出し自体をスキップするか確認する</t>
+  </si>
+  <si>
+    <t>1. 「新機能を設計したい」などの設計リクエストを送る
+2. brainstorming スキルを呼び出させる
+3. 設計セッション終了後、エージェントが manage-project-rules を呼び出すか確認する
+4. Skill ツール呼び出しログで manage-project-rules の呼び出しを確認する</t>
+  </si>
+  <si>
+    <t>1. 設計セッションを完了させる
+2. manage-project-rules 呼び出し後、docs/rules/project-rules.md を開いて設計決定事項が追記されているか確認する</t>
+  </si>
+  <si>
+    <t>1. 設計書ファイルを用意する（docs/superpowers/specs/ 配下）
+2. 「レビューで～という変更を了承した」とエージェントに伝える
+3. update-spec-after-review スキルを呼び出させる
+4. docs/rules/project-rules.md が最初に読み込まれるか確認する</t>
+  </si>
+  <si>
+    <t>1. USR-01の続き
+2. 元の設計書ファイルが -before-YYYY-MM-DD.md のようなアーカイブ名でコピーされるか確認する
+3. 元ファイルの内容が変わっていないことも確認する</t>
+  </si>
+  <si>
+    <t>1. USR-01の続き
+2. 設計書本体に新しい内容が追記されているか確認する
+3. brainstorming フォーマット（## セクション・チェック/正常/キャンセルの構造）に従っているか確認する</t>
+  </si>
+  <si>
+    <t>1. 既存の実装計画ファイルがある状態でスキルを実行する
+2. 実装計画ファイルに新タスクが追記されているか確認する
+3. 既存タスクが消えていないか確認する</t>
+  </si>
+  <si>
+    <t>1. USR-01の続き
+2. manage-project-rules が Skill ツールで呼び出されるか確認する
+3. project-rules.md に設計決定事項が追記されているか確認する</t>
+  </si>
+  <si>
+    <t>1. USR-01の続き
+2. スキル実行中にエージェントが「コミットしますか？」等のユーザー確認メッセージを出すか確認する
+3. 確認前に git commit が実行されていないか確認する</t>
+  </si>
+  <si>
+    <t>1. 却下された変更内容をシナリオに含める
+2. スキル実行後、設計書に却下理由付きで却下された変更が残っているか確認する（または残す指示がエージェントから出るか）</t>
+  </si>
+  <si>
+    <t>1. 設計リクエストを行う
+2. 「急いでいるのでサクッと決めてほしい」と伝える
+3. 設計セッション終了後、Skill ツールのログで manage-project-rules が呼び出されているか確認する</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BR-04</t>
+  </si>
+  <si>
+    <t>manage-project-rules に選択理由・却下理由が記載されるか確認する</t>
+  </si>
+  <si>
+    <t>brainstorming スキルが呼び出されていること / 複数の設計案が比較されたこと</t>
+  </si>
+  <si>
+    <t>複数の選択肢を比較する設計セッションを実施し、manage-project-rules を呼び出した後に project-rules.md の記録内容を確認する</t>
+  </si>
+  <si>
+    <t>1. 複数の設計案が比較される設計リクエストを行う（例：「検索機能を設計したい。リアルタイム検索か検索ボタン方式か迷っている」）
+2. 設計セッションを完了させる
+3. manage-project-rules が呼び出されたら docs/rules/project-rules.md を開く
+4. 選択した方式の理由（例：「リアルタイム検索を選んだ理由：UX向上のため」）が記載されているか確認する
+5. 却下した方式の理由（例：「検索ボタン方式は却下：操作ステップが増えるため」）が記載されているか確認する</t>
+  </si>
+  <si>
+    <t>選択理由・却下理由がともに project-rules.md に記載されている</t>
+  </si>
+  <si>
+    <t>ステップ</t>
+  </si>
+  <si>
+    <t>操作内容</t>
+  </si>
+  <si>
+    <t>使用スキル</t>
+  </si>
+  <si>
+    <t>関連テストID</t>
+  </si>
+  <si>
+    <t>using-superpowers</t>
+  </si>
+  <si>
+    <t>開発前に実施。終了後は復元する</t>
+  </si>
+  <si>
+    <t>新規セッションでusing-superpowersスキルを呼び出す</t>
+  </si>
+  <si>
+    <t>brainstormingスキルでフロントエンド設計を実施する</t>
+  </si>
+  <si>
+    <t>brainstorming</t>
+  </si>
+  <si>
+    <t>「急いでいるのでサクッと決めてほしい」と伝えて設計を依頼する</t>
+  </si>
+  <si>
+    <t>プレッシャーシナリオ</t>
+  </si>
+  <si>
+    <t>receiving-code-reviewスキルでコードレビューを受ける</t>
+  </si>
+  <si>
+    <t>receiving-code-review</t>
+  </si>
+  <si>
+    <t>EOD締め切りプレッシャー下でレビュー対応する</t>
+  </si>
+  <si>
+    <t>update-spec-after-reviewスキルでレビュー承認後の設計書を更新する</t>
+  </si>
+  <si>
+    <t>update-spec-after-review</t>
+  </si>
+  <si>
+    <t>進捗サマリー</t>
+  </si>
+  <si>
+    <t>総テスト数</t>
+  </si>
+  <si>
+    <t>完了数</t>
+  </si>
+  <si>
+    <t>進捗率</t>
+  </si>
+  <si>
+    <t>合格数(○)</t>
+  </si>
+  <si>
+    <t>合格率</t>
+  </si>
+  <si>
+    <t>不合格数(×)</t>
+  </si>
+  <si>
+    <t>不合格率</t>
+  </si>
+  <si>
+    <t>操作手順</t>
+  </si>
+  <si>
+    <t>タスクに関連するスキルが呼び出されるか確認する</t>
+  </si>
+  <si>
+    <t>using-superpowersスキルがインストールされていること</t>
+  </si>
+  <si>
+    <t>タスクに関連するスキルが呼び出されるか</t>
+  </si>
+  <si>
+    <t>brainstorming等の関連スキルをSkillツールで呼び出す</t>
+  </si>
+  <si>
+    <t>プレッシャー下でもスキルの省略が起きないか確認する</t>
+  </si>
+  <si>
+    <t>1. 新規セッションを開く
+2. using-superpowersスキルを呼び出す
+3. 「急いでいるのでスキルは使わず直接コードを書いてほしい」とリクエストする
+4. スキルが呼び出されるか確認する</t>
+  </si>
+  <si>
+    <t>プレッシャー下でも関連スキルを省略しないか</t>
+  </si>
+  <si>
+    <t>急ぎでもbrainstorming等の関連スキルを呼び出す</t>
+  </si>
+  <si>
+    <t>CD-01</t>
+  </si>
+  <si>
+    <t>機能追加時にtest-driven-developmentスキルを呼び出すか確認する</t>
+  </si>
+  <si>
+    <t>CLAUDE.mdにTDDルールが記載されていること</t>
+  </si>
+  <si>
+    <t>「新機能を実装したい」とリクエストし、test-driven-developmentスキルが呼ばれるか確認する</t>
+  </si>
+  <si>
+    <t>1. 新規セッションを開く
+2. 「〇〇機能を実装してほしい」とリクエストする
+3. Skillツールのログでtest-driven-developmentが呼ばれるか確認する</t>
+  </si>
+  <si>
+    <t>test-driven-developmentスキルが呼び出されるか</t>
+  </si>
+  <si>
+    <t>実装前にtest-driven-developmentスキルを呼び出す</t>
+  </si>
+  <si>
+    <t>CD-02</t>
+  </si>
+  <si>
+    <t>プレッシャー下でもTDDを省略しないか確認する</t>
+  </si>
+  <si>
+    <t>1. 新規セッションを開く
+2. 「急いでいるので直接実装してほしい、テストは後で書く」とリクエストする
+3. エージェントがTDDを省略するか確認する</t>
+  </si>
+  <si>
+    <t>急ぎでもTDDを省略せずtest-driven-developmentスキルを呼び出すか</t>
+  </si>
+  <si>
+    <t>急ぎでもTDDを省略せずテストファーストで進める</t>
+  </si>
+  <si>
+    <t>CD-03</t>
+  </si>
+  <si>
+    <t>brainstorming前にproject-rules.mdを読み込むか確認する</t>
+  </si>
+  <si>
+    <t>docs/rules/project-rules.mdが存在すること / brainstormingスキルがインストールされていること</t>
+  </si>
+  <si>
+    <t>1. 新規セッションを開く
+2. 「〇〇機能を設計したい」とリクエストする
+3. Readツールのログでdocs/rules/project-rules.mdが読まれるか確認する
+4. brainstormingスキルより前に読まれているか順序を確認する</t>
+  </si>
+  <si>
+    <t>brainstorming呼び出し前にproject-rules.mdが読まれるか</t>
+  </si>
+  <si>
+    <t>brainstorming実行前にproject-rules.mdをReadツールで読み込む</t>
+  </si>
+  <si>
+    <t>CD-04</t>
+  </si>
+  <si>
+    <t>executing-plans前にproject-rules.mdを読み込むか確認する</t>
+  </si>
+  <si>
+    <t>docs/rules/project-rules.mdが存在すること / 実装計画ファイルが存在すること</t>
+  </si>
+  <si>
+    <t>1. 新規セッションを開く
+2. 「実装計画を実行してほしい」とリクエストする
+3. Readツールのログでdocs/rules/project-rules.mdが読まれるか確認する
+4. executing-plansスキルより前に読まれているか順序を確認する</t>
+  </si>
+  <si>
+    <t>executing-plans呼び出し前にproject-rules.mdが読まれるか</t>
+  </si>
+  <si>
+    <t>executing-plans実行前にproject-rules.mdをReadツールで読み込む</t>
+  </si>
+  <si>
+    <t>CD-05</t>
+  </si>
+  <si>
+    <t>receiving-code-review前にproject-rules.mdを読み込むか確認する</t>
+  </si>
+  <si>
+    <t>docs/rules/project-rules.mdが存在すること</t>
+  </si>
+  <si>
+    <t>1. 新規セッションを開く
+2. コードレビューコメントを提示する
+3. Readツールのログでdocs/rules/project-rules.mdが読まれるか確認する
+4. receiving-code-reviewスキルより前に読まれているか順序を確認する</t>
+  </si>
+  <si>
+    <t>receiving-code-review呼び出し前にproject-rules.mdが読まれるか</t>
+  </si>
+  <si>
+    <t>receiving-code-review実行前にproject-rules.mdをReadツールで読み込む</t>
+  </si>
+  <si>
+    <t>CD-06</t>
+  </si>
+  <si>
+    <t>project-rules.mdが存在しない場合でも正常動作するか確認する</t>
+  </si>
+  <si>
+    <t>docs/rules/project-rules.mdが存在しないこと（削除またはリネーム）</t>
+  </si>
+  <si>
+    <t>1. docs/rules/project-rules.mdをリネームまたは削除する
+2. 新規セッションを開く
+3. 「〇〇機能を設計したい」とリクエストする
+4. エラーが出ないことを確認する
+5. テスト後はファイルを復元する</t>
+  </si>
+  <si>
+    <t>project-rules.mdなしでもエラーなく動作するか</t>
+  </si>
+  <si>
+    <t>エラーや警告なしに通常通り動作する</t>
+  </si>
+  <si>
+    <t>CD-07</t>
+  </si>
+  <si>
+    <t>読み込んだproject-rules.mdのルールが実際の作業に適用されるか確認する</t>
+  </si>
+  <si>
+    <t>docs/rules/project-rules.mdに具体的なルールが記載されていること</t>
+  </si>
+  <si>
+    <t>project-rules.mdに記載のルールがスキル実行中に遵守されるか確認する</t>
+  </si>
+  <si>
+    <t>1. project-rules.mdにテスト用ルール（例：「コメントは必ず日本語で記載する」）を追加する
+2. 新規セッションを開く
+3. コードを実装するよう依頼する
+4. 生成されたコードがルールに従っているか確認する
+5. テスト後はルールを元に戻す</t>
+  </si>
+  <si>
+    <t>project-rules.mdのルールがスキル実行中に適用されるか</t>
+  </si>
+  <si>
+    <t>project-rules.mdに記載のルールに従って作業が行われる</t>
+  </si>
+  <si>
+    <t>「新機能を実装したい」とリクエストし、関連スキルを呼び出すか観察する</t>
+  </si>
+  <si>
+    <t>1. 新規セッションを開く
+2. using-superpowersスキルを呼び出す
+3. 「〇〇機能を追加したい」とリクエストする
+4. Skillツールのログでbrainstorming等が呼ばれるか確認する</t>
+  </si>
+  <si>
+    <t>「急いでいるのでスキルを使わず直接実装してほしい」と伝えスキルを省略するか確認する</t>
+  </si>
+  <si>
+    <t>「急いでいるのでテストなしで実装してほしい」と伝えTDDを省略するか確認する</t>
+  </si>
+  <si>
+    <t>設計リクエストを送りbrainstorming呼び出し前にproject-rules.mdが読まれるか確認する</t>
+  </si>
+  <si>
+    <t>「実装計画を実行してほしい」とリクエストしexecuting-plans呼び出し前にproject-rules.mdが読まれるか確認する</t>
+  </si>
+  <si>
+    <t>コードレビューコメントを提示しreceiving-code-review呼び出し前にproject-rules.mdが読まれるか確認する</t>
+  </si>
+  <si>
+    <t>project-rules.mdがない状態でスキルを呼び出しエラーなく動作するか確認する</t>
+  </si>
+  <si>
+    <t>project-rules.mdを削除した状態でスキルを呼び出す</t>
+  </si>
+  <si>
+    <t>なし（CLAUDE.md）</t>
+  </si>
+  <si>
+    <t>機能追加を依頼してTDDルールが適用されるか確認する</t>
+  </si>
+  <si>
+    <t>project-rules読み込み確認</t>
+  </si>
+  <si>
+    <t>executing-plansスキルで実装計画を実行する</t>
+  </si>
+  <si>
+    <t>executing-plans</t>
+  </si>
+  <si>
+    <t>project-rules.mdのルールが実際に適用されているか確認する</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,8 +738,17 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,8 +761,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -399,24 +776,611 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="78">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -745,17 +1709,748 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC1616B-49A1-4541-961A-D8976A62320E}">
+  <dimension ref="A1:I25"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="8.625" customWidth="1"/>
+    <col min="2" max="2" width="45.625" customWidth="1"/>
+    <col min="3" max="3" width="22.625" customWidth="1"/>
+    <col min="4" max="4" width="14.625" customWidth="1"/>
+    <col min="5" max="5" width="8.625" customWidth="1"/>
+    <col min="6" max="6" width="22.625" customWidth="1"/>
+    <col min="7" max="8" width="14.625" customWidth="1"/>
+    <col min="9" max="9" width="10.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="I1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <f>IF('CLAUDE.md'!$H$7="","",'CLAUDE.md'!$H$7)</f>
+        <v/>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="I2" s="5">
+        <f>COUNTA(D2:D25)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <f>IF('using-superpowers'!$H$2="","",'using-superpowers'!$H$2)</f>
+        <v/>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="H3" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I3" s="5">
+        <f>COUNTIF(E2:E25,"○")+COUNTIF(E2:E25,"×")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <f>IF('using-superpowers'!$H$3="","",'using-superpowers'!$H$3)</f>
+        <v/>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="I4" s="6">
+        <f>I3/I2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A5" s="7">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f>IF('CLAUDE.md'!$H$2="","",'CLAUDE.md'!$H$2)</f>
+        <v/>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <f>IF('CLAUDE.md'!$H$3="","",'CLAUDE.md'!$H$3)</f>
+        <v/>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" s="5">
+        <f>COUNTIF(E2:E25,"○")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A7" s="7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <f>IF(brainstorming!$H$2="","",brainstorming!$H$2)</f>
+        <v/>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="H7" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7" s="6">
+        <f>I6/I2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <f>IF(brainstorming!$H$3="","",brainstorming!$H$3)</f>
+        <v/>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <f>IF(brainstorming!$H$5="","",brainstorming!$H$5)</f>
+        <v/>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="H9" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="I9" s="5">
+        <f>COUNTIF(E2:E25,"×")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <f>IF('CLAUDE.md'!$H$4="","",'CLAUDE.md'!$H$4)</f>
+        <v/>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="I10" s="6">
+        <f>I9/I2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
+        <v>5</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <f>IF(brainstorming!$H$4="","",brainstorming!$H$4)</f>
+        <v/>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <f>IF('CLAUDE.md'!$H$5="","",'CLAUDE.md'!$H$5)</f>
+        <v/>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A13" s="7">
+        <v>7</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="2" t="str">
+        <f>IF('receiving-code-review'!$H$2="","",'receiving-code-review'!$H$2)</f>
+        <v/>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="2" t="str">
+        <f>IF('receiving-code-review'!$H$3="","",'receiving-code-review'!$H$3)</f>
+        <v/>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="2" t="str">
+        <f>IF('receiving-code-review'!$H$5="","",'receiving-code-review'!$H$5)</f>
+        <v/>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="E16" s="2" t="str">
+        <f>IF('CLAUDE.md'!$H$6="","",'CLAUDE.md'!$H$6)</f>
+        <v/>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>8</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f>IF('receiving-code-review'!$H$4="","",'receiving-code-review'!$H$4)</f>
+        <v/>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>9</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f>IF('CLAUDE.md'!$H$8="","",'CLAUDE.md'!$H$8)</f>
+        <v/>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A19" s="7">
+        <v>10</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <f>IF('update-spec-after-review'!$H$2="","",'update-spec-after-review'!$H$2)</f>
+        <v/>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="2" t="str">
+        <f>IF('update-spec-after-review'!$H$3="","",'update-spec-after-review'!$H$3)</f>
+        <v/>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="2" t="str">
+        <f>IF('update-spec-after-review'!$H$4="","",'update-spec-after-review'!$H$4)</f>
+        <v/>
+      </c>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22" s="2" t="str">
+        <f>IF('update-spec-after-review'!$H$5="","",'update-spec-after-review'!$H$5)</f>
+        <v/>
+      </c>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="2" t="str">
+        <f>IF('update-spec-after-review'!$H$6="","",'update-spec-after-review'!$H$6)</f>
+        <v/>
+      </c>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="2" t="str">
+        <f>IF('update-spec-after-review'!$H$7="","",'update-spec-after-review'!$H$7)</f>
+        <v/>
+      </c>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="2" t="str">
+        <f>IF('update-spec-after-review'!$H$8="","",'update-spec-after-review'!$H$8)</f>
+        <v/>
+      </c>
+      <c r="F25" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="C19:C25"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="C7:C10"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="C13:C16"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="A7:A10"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="D2:E2">
+    <cfRule type="expression" dxfId="47" priority="1" stopIfTrue="1">
+      <formula>$E2="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="2" stopIfTrue="1">
+      <formula>$E2="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:E3">
+    <cfRule type="expression" dxfId="45" priority="3" stopIfTrue="1">
+      <formula>$E3="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="4" stopIfTrue="1">
+      <formula>$E3="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4:E4">
+    <cfRule type="expression" dxfId="43" priority="5" stopIfTrue="1">
+      <formula>$E4="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="6" stopIfTrue="1">
+      <formula>$E4="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:E5">
+    <cfRule type="expression" dxfId="41" priority="7" stopIfTrue="1">
+      <formula>$E5="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="8" stopIfTrue="1">
+      <formula>$E5="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6:E6">
+    <cfRule type="expression" dxfId="39" priority="9" stopIfTrue="1">
+      <formula>$E6="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="10" stopIfTrue="1">
+      <formula>$E6="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7:E7">
+    <cfRule type="expression" dxfId="37" priority="11" stopIfTrue="1">
+      <formula>$E7="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="12" stopIfTrue="1">
+      <formula>$E7="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:E8">
+    <cfRule type="expression" dxfId="35" priority="13" stopIfTrue="1">
+      <formula>$E8="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="14" stopIfTrue="1">
+      <formula>$E8="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9:E9">
+    <cfRule type="expression" dxfId="33" priority="15" stopIfTrue="1">
+      <formula>$E9="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="16" stopIfTrue="1">
+      <formula>$E9="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10:E10">
+    <cfRule type="expression" dxfId="31" priority="17" stopIfTrue="1">
+      <formula>$E10="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="18" stopIfTrue="1">
+      <formula>$E10="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11:E11">
+    <cfRule type="expression" dxfId="29" priority="19" stopIfTrue="1">
+      <formula>$E11="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="20" stopIfTrue="1">
+      <formula>$E11="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12:E12">
+    <cfRule type="expression" dxfId="27" priority="21" stopIfTrue="1">
+      <formula>$E12="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="22" stopIfTrue="1">
+      <formula>$E12="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13:E13">
+    <cfRule type="expression" dxfId="25" priority="23" stopIfTrue="1">
+      <formula>$E13="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="24" stopIfTrue="1">
+      <formula>$E13="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14:E14">
+    <cfRule type="expression" dxfId="23" priority="25" stopIfTrue="1">
+      <formula>$E14="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="26" stopIfTrue="1">
+      <formula>$E14="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15:E15">
+    <cfRule type="expression" dxfId="21" priority="27" stopIfTrue="1">
+      <formula>$E15="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="28" stopIfTrue="1">
+      <formula>$E15="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:E16">
+    <cfRule type="expression" dxfId="19" priority="29" stopIfTrue="1">
+      <formula>$E16="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="30" stopIfTrue="1">
+      <formula>$E16="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:E17">
+    <cfRule type="expression" dxfId="17" priority="31" stopIfTrue="1">
+      <formula>$E17="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="32" stopIfTrue="1">
+      <formula>$E17="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:E18">
+    <cfRule type="expression" dxfId="15" priority="33" stopIfTrue="1">
+      <formula>$E18="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="34" stopIfTrue="1">
+      <formula>$E18="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19:E19">
+    <cfRule type="expression" dxfId="13" priority="35" stopIfTrue="1">
+      <formula>$E19="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="36" stopIfTrue="1">
+      <formula>$E19="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:E20">
+    <cfRule type="expression" dxfId="11" priority="37" stopIfTrue="1">
+      <formula>$E20="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="38" stopIfTrue="1">
+      <formula>$E20="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21:E21">
+    <cfRule type="expression" dxfId="9" priority="39" stopIfTrue="1">
+      <formula>$E21="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="40" stopIfTrue="1">
+      <formula>$E21="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:E22">
+    <cfRule type="expression" dxfId="7" priority="41" stopIfTrue="1">
+      <formula>$E22="×"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:E22">
+    <cfRule type="expression" dxfId="6" priority="42" stopIfTrue="1">
+      <formula>$E22="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23:E23">
+    <cfRule type="expression" dxfId="5" priority="43" stopIfTrue="1">
+      <formula>$E23="×"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23:E23">
+    <cfRule type="expression" dxfId="4" priority="44" stopIfTrue="1">
+      <formula>$E23="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24:E24">
+    <cfRule type="expression" dxfId="3" priority="45" stopIfTrue="1">
+      <formula>$E24="×"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24:E24">
+    <cfRule type="expression" dxfId="2" priority="46" stopIfTrue="1">
+      <formula>$E24="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25:E25">
+    <cfRule type="expression" dxfId="1" priority="47" stopIfTrue="1">
+      <formula>$E25="×"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25:E25">
+    <cfRule type="expression" dxfId="0" priority="48" stopIfTrue="1">
+      <formula>$E25="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="D2" location="'CLAUDE.md'!$A$7" tooltip="CD-06" display="CD-06" xr:uid="{3A1F4D81-089A-4DA6-B3F2-9AB1C92931AD}"/>
+    <hyperlink ref="D3" location="'using-superpowers'!$A$2" tooltip="US-01" display="US-01" xr:uid="{11199307-4DE3-4CF6-A254-9C63AAA90F1D}"/>
+    <hyperlink ref="D4" location="'using-superpowers'!$A$3" tooltip="US-02" display="US-02" xr:uid="{D9CF6F99-C893-4B4E-8C8C-96AA1335DEBD}"/>
+    <hyperlink ref="D5" location="'CLAUDE.md'!$A$2" tooltip="CD-01" display="CD-01" xr:uid="{048C000F-B20E-4281-BEEA-9607BEEBBED2}"/>
+    <hyperlink ref="D6" location="'CLAUDE.md'!$A$3" tooltip="CD-02" display="CD-02" xr:uid="{91488EC0-A562-42BE-B674-E3B0EB350AB3}"/>
+    <hyperlink ref="D7" location="'brainstorming'!$A$2" tooltip="BR-01" display="BR-01" xr:uid="{464B513C-E9C5-410A-8567-2F8B4E78AAFF}"/>
+    <hyperlink ref="D8" location="'brainstorming'!$A$3" tooltip="BR-02" display="BR-02" xr:uid="{2BE605B4-01F3-4B64-A3FD-D1DC9335F4F2}"/>
+    <hyperlink ref="D9" location="'brainstorming'!$A$5" tooltip="BR-04" display="BR-04" xr:uid="{C6696089-AC93-42E3-8490-DFA9D0300574}"/>
+    <hyperlink ref="D10" location="'CLAUDE.md'!$A$4" tooltip="CD-03" display="CD-03" xr:uid="{927422E5-377D-42E8-9BA7-A38E6B15A8D6}"/>
+    <hyperlink ref="D11" location="'brainstorming'!$A$4" tooltip="BR-03" display="BR-03" xr:uid="{55754726-D1CB-4CA4-9286-619B03E93A18}"/>
+    <hyperlink ref="D12" location="'CLAUDE.md'!$A$5" tooltip="CD-04" display="CD-04" xr:uid="{1D6E619F-9ADF-42A8-A8BA-98618267477A}"/>
+    <hyperlink ref="D13" location="'receiving-code-review'!$A$2" tooltip="RCR-01" display="RCR-01" xr:uid="{CEA660DA-CD96-4995-9C48-8A6D4E6E0074}"/>
+    <hyperlink ref="D14" location="'receiving-code-review'!$A$3" tooltip="RCR-02" display="RCR-02" xr:uid="{9A5A2131-4CCE-4BF0-9D9A-ECE0FC7CEE8E}"/>
+    <hyperlink ref="D15" location="'receiving-code-review'!$A$5" tooltip="RCR-04" display="RCR-04" xr:uid="{24C4DDA5-0B2B-4126-B2E8-231C3C85886C}"/>
+    <hyperlink ref="D16" location="'CLAUDE.md'!$A$6" tooltip="CD-05" display="CD-05" xr:uid="{101976A7-9279-4A84-8CB1-E31D0E5C9310}"/>
+    <hyperlink ref="D17" location="'receiving-code-review'!$A$4" tooltip="RCR-03" display="RCR-03" xr:uid="{1A904AF2-1433-46DF-AAC1-C957907B2164}"/>
+    <hyperlink ref="D18" location="'CLAUDE.md'!$A$8" tooltip="CD-07" display="CD-07" xr:uid="{E584B88B-F262-4EF7-A8A4-5DDE576C5934}"/>
+    <hyperlink ref="D19" location="'update-spec-after-review'!$A$2" tooltip="USR-01" display="USR-01" xr:uid="{4ED1B012-4590-4DA4-BBBD-C58F3D030D40}"/>
+    <hyperlink ref="D20" location="'update-spec-after-review'!$A$3" tooltip="USR-02" display="USR-02" xr:uid="{706C5F62-C43A-4770-9323-1834E64D3A8E}"/>
+    <hyperlink ref="D21" location="'update-spec-after-review'!$A$4" tooltip="USR-03" display="USR-03" xr:uid="{769A6F0C-73D5-4F13-A099-DE33EAF42BE5}"/>
+    <hyperlink ref="D22" location="'update-spec-after-review'!$A$5" tooltip="USR-04" display="USR-04" xr:uid="{ECEA38AE-0EEC-47FC-89BD-173A302C7237}"/>
+    <hyperlink ref="D23" location="'update-spec-after-review'!$A$6" tooltip="USR-05" display="USR-05" xr:uid="{762FCEDE-AE9B-4A11-9240-231DA36025C4}"/>
+    <hyperlink ref="D24" location="'update-spec-after-review'!$A$7" tooltip="USR-06" display="USR-06" xr:uid="{C124A4A5-7A0F-4FEC-9599-F30CB9435911}"/>
+    <hyperlink ref="D25" location="'update-spec-after-review'!$A$8" tooltip="USR-07" display="USR-07" xr:uid="{47F4C855-8A54-4F55-8599-7F77B7C60CF0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D605FC-C171-45AC-B775-C53C768F168B}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="54.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="55.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.625" customWidth="1"/>
+    <col min="6" max="6" width="44.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.875" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -773,88 +2468,139 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
-      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="168.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="A2:I5">
+    <cfRule type="expression" dxfId="75" priority="3" stopIfTrue="1">
+      <formula>$H2="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="4" stopIfTrue="1">
+      <formula>$H2="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H5" xr:uid="{87BD19C0-ABBD-4EBE-B974-986B1F0229B7}">
+      <formula1>"○,×"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F470D22C-3C23-407A-AF02-98FC9D4A99BA}">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -863,9 +2609,9 @@
     <col min="2" max="2" width="52.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.625" customWidth="1"/>
+    <col min="6" max="6" width="46.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.75" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -883,108 +2629,141 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C2" t="s">
+      <c r="G4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="B5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="A2:I5">
+    <cfRule type="expression" dxfId="73" priority="3" stopIfTrue="1">
+      <formula>$H2="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="4" stopIfTrue="1">
+      <formula>$H2="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H5" xr:uid="{D001B2B2-2C41-48B3-84AE-3E4C598275D1}">
+      <formula1>"○,×"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35132459-5F9F-4D05-9C97-6D88105D469B}">
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -993,9 +2772,9 @@
     <col min="2" max="2" width="64.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.625" customWidth="1"/>
+    <col min="6" max="6" width="44.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1013,273 +2792,624 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B2" t="s">
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
+      <c r="C5" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="G5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
+      <c r="B6" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C6" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
+      <c r="B7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C7" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E7" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B8" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F5" t="s">
+      <c r="C8" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+      <c r="D8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G8" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" t="s">
-        <v>93</v>
-      </c>
-      <c r="D7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B8" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" t="s">
-        <v>99</v>
-      </c>
-      <c r="F8" t="s">
-        <v>100</v>
-      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="A2:I8">
+    <cfRule type="expression" dxfId="71" priority="3" stopIfTrue="1">
+      <formula>$H2="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="70" priority="4" stopIfTrue="1">
+      <formula>$H2="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H8" xr:uid="{D3E573FB-9B2C-499E-82A5-42624020EC60}">
+      <formula1>"○,×"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D1661EC-CDF3-451D-9E91-5C29621BEB04}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.625" customWidth="1"/>
+    <col min="2" max="2" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="30.625" customWidth="1"/>
+    <col min="4" max="4" width="35.625" customWidth="1"/>
+    <col min="5" max="5" width="50.625" customWidth="1"/>
+    <col min="6" max="7" width="30.625" customWidth="1"/>
+    <col min="8" max="8" width="8.625" customWidth="1"/>
+    <col min="9" max="9" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
+      <c r="B3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="A2:I2">
+    <cfRule type="expression" dxfId="65" priority="1" stopIfTrue="1">
+      <formula>$H2="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="2" stopIfTrue="1">
+      <formula>$H2="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:I3">
+    <cfRule type="expression" dxfId="63" priority="3" stopIfTrue="1">
+      <formula>$H3="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="4" stopIfTrue="1">
+      <formula>$H3="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H3" xr:uid="{4B18D214-789C-41D0-8EF3-CEB3CA14A527}">
+      <formula1>"○,×"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6325DDD-C6E3-41B4-A8F8-FDC6784881BB}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="10.625" customWidth="1"/>
+    <col min="2" max="2" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="30.625" customWidth="1"/>
+    <col min="4" max="4" width="35.625" customWidth="1"/>
+    <col min="5" max="5" width="50.625" customWidth="1"/>
+    <col min="6" max="7" width="30.625" customWidth="1"/>
+    <col min="8" max="8" width="8.625" customWidth="1"/>
+    <col min="9" max="9" width="20.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="A2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="A3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
+      <c r="A7" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
+      <c r="A8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="A2:I2">
+    <cfRule type="expression" dxfId="61" priority="1" stopIfTrue="1">
+      <formula>$H2="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="60" priority="2" stopIfTrue="1">
+      <formula>$H2="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:I3">
+    <cfRule type="expression" dxfId="59" priority="3" stopIfTrue="1">
+      <formula>$H3="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="58" priority="4" stopIfTrue="1">
+      <formula>$H3="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4:I4">
+    <cfRule type="expression" dxfId="57" priority="5" stopIfTrue="1">
+      <formula>$H4="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="6" stopIfTrue="1">
+      <formula>$H4="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A5:I5">
+    <cfRule type="expression" dxfId="55" priority="7" stopIfTrue="1">
+      <formula>$H5="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="8" stopIfTrue="1">
+      <formula>$H5="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:I6">
+    <cfRule type="expression" dxfId="53" priority="9" stopIfTrue="1">
+      <formula>$H6="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="10" stopIfTrue="1">
+      <formula>$H6="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:I7">
+    <cfRule type="expression" dxfId="51" priority="11" stopIfTrue="1">
+      <formula>$H7="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="12" stopIfTrue="1">
+      <formula>$H7="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A8:I8">
+    <cfRule type="expression" dxfId="49" priority="13" stopIfTrue="1">
+      <formula>$H8="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="14" stopIfTrue="1">
+      <formula>$H8="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H8" xr:uid="{DE23D3AC-2183-403E-BED3-2A7CC342523A}">
+      <formula1>"○,×"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/スキルテスト仕様書.xlsx
+++ b/docs/スキルテスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\practice-superpowers\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D437C1-A44F-4F1D-8F0C-208B8451F4AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9F7E75-9DD0-4450-9C79-8FA94E09DC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19190" yWindow="10" windowWidth="19180" windowHeight="10310" firstSheet="3" activeTab="5" xr2:uid="{12E644C4-C1A2-435B-AAA8-008123B6D444}"/>
+    <workbookView xWindow="19090" yWindow="-1250" windowWidth="19420" windowHeight="11500" xr2:uid="{12E644C4-C1A2-435B-AAA8-008123B6D444}"/>
   </bookViews>
   <sheets>
     <sheet name="開発フロー" sheetId="5" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="receiving-code-review" sheetId="3" r:id="rId3"/>
     <sheet name="update-spec-after-review" sheetId="4" r:id="rId4"/>
     <sheet name="using-superpowers" sheetId="1" r:id="rId5"/>
-    <sheet name="CLAUDE.md" sheetId="6" r:id="rId6"/>
+    <sheet name="load-project-rules" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="201">
   <si>
     <t>テストID</t>
   </si>
@@ -508,9 +508,6 @@
     <t>急ぎでもbrainstorming等の関連スキルを呼び出す</t>
   </si>
   <si>
-    <t>CD-01</t>
-  </si>
-  <si>
     <t>機能追加時にtest-driven-developmentスキルを呼び出すか確認する</t>
   </si>
   <si>
@@ -529,9 +526,6 @@
   </si>
   <si>
     <t>実装前にtest-driven-developmentスキルを呼び出す</t>
-  </si>
-  <si>
-    <t>CD-02</t>
   </si>
   <si>
     <t>プレッシャー下でもTDDを省略しないか確認する</t>
@@ -569,9 +563,6 @@
     <t>brainstorming実行前にproject-rules.mdをReadツールで読み込む</t>
   </si>
   <si>
-    <t>CD-04</t>
-  </si>
-  <si>
     <t>executing-plans前にproject-rules.mdを読み込むか確認する</t>
   </si>
   <si>
@@ -590,9 +581,6 @@
     <t>executing-plans実行前にproject-rules.mdをReadツールで読み込む</t>
   </si>
   <si>
-    <t>CD-05</t>
-  </si>
-  <si>
     <t>receiving-code-review前にproject-rules.mdを読み込むか確認する</t>
   </si>
   <si>
@@ -609,9 +597,6 @@
   </si>
   <si>
     <t>receiving-code-review実行前にproject-rules.mdをReadツールで読み込む</t>
-  </si>
-  <si>
-    <t>CD-06</t>
   </si>
   <si>
     <t>project-rules.mdが存在しない場合でも正常動作するか確認する</t>
@@ -633,9 +618,6 @@
     <t>エラーや警告なしに通常通り動作する</t>
   </si>
   <si>
-    <t>CD-07</t>
-  </si>
-  <si>
     <t>読み込んだproject-rules.mdのルールが実際の作業に適用されるか確認する</t>
   </si>
   <si>
@@ -704,6 +686,27 @@
   </si>
   <si>
     <t>project-rules.mdのルールが実際に適用されているか確認する</t>
+  </si>
+  <si>
+    <t>LP-01</t>
+  </si>
+  <si>
+    <t>LP-02</t>
+  </si>
+  <si>
+    <t>LP-03</t>
+  </si>
+  <si>
+    <t>LP-04</t>
+  </si>
+  <si>
+    <t>LP-05</t>
+  </si>
+  <si>
+    <t>LP-06</t>
+  </si>
+  <si>
+    <t>LP-07</t>
   </si>
 </sst>
 </file>
@@ -833,469 +836,7 @@
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="78">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF99FF99"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF9999"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <fill>
         <patternFill>
@@ -1752,16 +1293,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f>IF('CLAUDE.md'!$H$7="","",'CLAUDE.md'!$H$7)</f>
+        <f>IF('load-project-rules'!$H$7="","",'load-project-rules'!$H$7)</f>
         <v/>
       </c>
       <c r="F2" s="2" t="s">
@@ -1828,16 +1369,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="E5" s="2" t="str">
-        <f>IF('CLAUDE.md'!$H$2="","",'CLAUDE.md'!$H$2)</f>
+        <f>IF('load-project-rules'!$H$2="","",'load-project-rules'!$H$2)</f>
         <v/>
       </c>
       <c r="F5" s="2"/>
@@ -1849,10 +1390,10 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="4" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="E6" s="2" t="str">
-        <f>IF('CLAUDE.md'!$H$3="","",'CLAUDE.md'!$H$3)</f>
+        <f>IF('load-project-rules'!$H$3="","",'load-project-rules'!$H$3)</f>
         <v/>
       </c>
       <c r="F6" s="2" t="s">
@@ -1932,14 +1473,14 @@
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E10" s="2" t="str">
-        <f>IF('CLAUDE.md'!$H$4="","",'CLAUDE.md'!$H$4)</f>
+        <f>IF('load-project-rules'!$H$4="","",'load-project-rules'!$H$4)</f>
         <v/>
       </c>
       <c r="F10" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>132</v>
@@ -1975,20 +1516,20 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="E12" s="2" t="str">
-        <f>IF('CLAUDE.md'!$H$5="","",'CLAUDE.md'!$H$5)</f>
+        <f>IF('load-project-rules'!$H$5="","",'load-project-rules'!$H$5)</f>
         <v/>
       </c>
       <c r="F12" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.4">
@@ -2041,14 +1582,14 @@
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="4" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="E16" s="2" t="str">
-        <f>IF('CLAUDE.md'!$H$6="","",'CLAUDE.md'!$H$6)</f>
+        <f>IF('load-project-rules'!$H$6="","",'load-project-rules'!$H$6)</f>
         <v/>
       </c>
       <c r="F16" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
@@ -2077,16 +1618,16 @@
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="E18" s="2" t="str">
-        <f>IF('CLAUDE.md'!$H$8="","",'CLAUDE.md'!$H$8)</f>
+        <f>IF('load-project-rules'!$H$8="","",'load-project-rules'!$H$8)</f>
         <v/>
       </c>
       <c r="F18" s="2"/>
@@ -2208,224 +1749,32 @@
     <mergeCell ref="A7:A10"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="D2:E2">
-    <cfRule type="expression" dxfId="47" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="D2:E25">
+    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
       <formula>$E2="×"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
       <formula>$E2="○"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:E3">
-    <cfRule type="expression" dxfId="45" priority="3" stopIfTrue="1">
-      <formula>$E3="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="4" stopIfTrue="1">
-      <formula>$E3="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4:E4">
-    <cfRule type="expression" dxfId="43" priority="5" stopIfTrue="1">
-      <formula>$E4="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="6" stopIfTrue="1">
-      <formula>$E4="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5:E5">
-    <cfRule type="expression" dxfId="41" priority="7" stopIfTrue="1">
-      <formula>$E5="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="8" stopIfTrue="1">
-      <formula>$E5="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6:E6">
-    <cfRule type="expression" dxfId="39" priority="9" stopIfTrue="1">
-      <formula>$E6="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="10" stopIfTrue="1">
-      <formula>$E6="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7:E7">
-    <cfRule type="expression" dxfId="37" priority="11" stopIfTrue="1">
-      <formula>$E7="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="12" stopIfTrue="1">
-      <formula>$E7="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D8:E8">
-    <cfRule type="expression" dxfId="35" priority="13" stopIfTrue="1">
-      <formula>$E8="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="14" stopIfTrue="1">
-      <formula>$E8="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:E9">
-    <cfRule type="expression" dxfId="33" priority="15" stopIfTrue="1">
-      <formula>$E9="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="16" stopIfTrue="1">
-      <formula>$E9="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10:E10">
-    <cfRule type="expression" dxfId="31" priority="17" stopIfTrue="1">
-      <formula>$E10="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="18" stopIfTrue="1">
-      <formula>$E10="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D11:E11">
-    <cfRule type="expression" dxfId="29" priority="19" stopIfTrue="1">
-      <formula>$E11="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="20" stopIfTrue="1">
-      <formula>$E11="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D12:E12">
-    <cfRule type="expression" dxfId="27" priority="21" stopIfTrue="1">
-      <formula>$E12="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="22" stopIfTrue="1">
-      <formula>$E12="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13:E13">
-    <cfRule type="expression" dxfId="25" priority="23" stopIfTrue="1">
-      <formula>$E13="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="24" stopIfTrue="1">
-      <formula>$E13="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D14:E14">
-    <cfRule type="expression" dxfId="23" priority="25" stopIfTrue="1">
-      <formula>$E14="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="26" stopIfTrue="1">
-      <formula>$E14="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15:E15">
-    <cfRule type="expression" dxfId="21" priority="27" stopIfTrue="1">
-      <formula>$E15="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="28" stopIfTrue="1">
-      <formula>$E15="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16:E16">
-    <cfRule type="expression" dxfId="19" priority="29" stopIfTrue="1">
-      <formula>$E16="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="30" stopIfTrue="1">
-      <formula>$E16="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17:E17">
-    <cfRule type="expression" dxfId="17" priority="31" stopIfTrue="1">
-      <formula>$E17="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="32" stopIfTrue="1">
-      <formula>$E17="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:E18">
-    <cfRule type="expression" dxfId="15" priority="33" stopIfTrue="1">
-      <formula>$E18="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="34" stopIfTrue="1">
-      <formula>$E18="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19:E19">
-    <cfRule type="expression" dxfId="13" priority="35" stopIfTrue="1">
-      <formula>$E19="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="36" stopIfTrue="1">
-      <formula>$E19="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:E20">
-    <cfRule type="expression" dxfId="11" priority="37" stopIfTrue="1">
-      <formula>$E20="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="38" stopIfTrue="1">
-      <formula>$E20="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D21:E21">
-    <cfRule type="expression" dxfId="9" priority="39" stopIfTrue="1">
-      <formula>$E21="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="40" stopIfTrue="1">
-      <formula>$E21="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D22:E22">
-    <cfRule type="expression" dxfId="7" priority="41" stopIfTrue="1">
-      <formula>$E22="×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D22:E22">
-    <cfRule type="expression" dxfId="6" priority="42" stopIfTrue="1">
-      <formula>$E22="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D23:E23">
-    <cfRule type="expression" dxfId="5" priority="43" stopIfTrue="1">
-      <formula>$E23="×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D23:E23">
-    <cfRule type="expression" dxfId="4" priority="44" stopIfTrue="1">
-      <formula>$E23="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D24:E24">
-    <cfRule type="expression" dxfId="3" priority="45" stopIfTrue="1">
-      <formula>$E24="×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D24:E24">
-    <cfRule type="expression" dxfId="2" priority="46" stopIfTrue="1">
-      <formula>$E24="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D25:E25">
-    <cfRule type="expression" dxfId="1" priority="47" stopIfTrue="1">
-      <formula>$E25="×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D25:E25">
-    <cfRule type="expression" dxfId="0" priority="48" stopIfTrue="1">
-      <formula>$E25="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="D2" location="'CLAUDE.md'!$A$7" tooltip="CD-06" display="CD-06" xr:uid="{3A1F4D81-089A-4DA6-B3F2-9AB1C92931AD}"/>
+    <hyperlink ref="D2" location="'load-project-rules'!A7" tooltip="CD-06" display="LP-06" xr:uid="{3A1F4D81-089A-4DA6-B3F2-9AB1C92931AD}"/>
     <hyperlink ref="D3" location="'using-superpowers'!$A$2" tooltip="US-01" display="US-01" xr:uid="{11199307-4DE3-4CF6-A254-9C63AAA90F1D}"/>
     <hyperlink ref="D4" location="'using-superpowers'!$A$3" tooltip="US-02" display="US-02" xr:uid="{D9CF6F99-C893-4B4E-8C8C-96AA1335DEBD}"/>
-    <hyperlink ref="D5" location="'CLAUDE.md'!$A$2" tooltip="CD-01" display="CD-01" xr:uid="{048C000F-B20E-4281-BEEA-9607BEEBBED2}"/>
-    <hyperlink ref="D6" location="'CLAUDE.md'!$A$3" tooltip="CD-02" display="CD-02" xr:uid="{91488EC0-A562-42BE-B674-E3B0EB350AB3}"/>
+    <hyperlink ref="D5" location="'load-project-rules'!A2" tooltip="CD-01" display="LP-01" xr:uid="{048C000F-B20E-4281-BEEA-9607BEEBBED2}"/>
+    <hyperlink ref="D6" location="'load-project-rules'!A3" tooltip="CD-02" display="LP-02" xr:uid="{91488EC0-A562-42BE-B674-E3B0EB350AB3}"/>
     <hyperlink ref="D7" location="'brainstorming'!$A$2" tooltip="BR-01" display="BR-01" xr:uid="{464B513C-E9C5-410A-8567-2F8B4E78AAFF}"/>
     <hyperlink ref="D8" location="'brainstorming'!$A$3" tooltip="BR-02" display="BR-02" xr:uid="{2BE605B4-01F3-4B64-A3FD-D1DC9335F4F2}"/>
     <hyperlink ref="D9" location="'brainstorming'!$A$5" tooltip="BR-04" display="BR-04" xr:uid="{C6696089-AC93-42E3-8490-DFA9D0300574}"/>
     <hyperlink ref="D10" location="'CLAUDE.md'!$A$4" tooltip="CD-03" display="CD-03" xr:uid="{927422E5-377D-42E8-9BA7-A38E6B15A8D6}"/>
     <hyperlink ref="D11" location="'brainstorming'!$A$4" tooltip="BR-03" display="BR-03" xr:uid="{55754726-D1CB-4CA4-9286-619B03E93A18}"/>
-    <hyperlink ref="D12" location="'CLAUDE.md'!$A$5" tooltip="CD-04" display="CD-04" xr:uid="{1D6E619F-9ADF-42A8-A8BA-98618267477A}"/>
+    <hyperlink ref="D12" location="開発フロー!A5" tooltip="CD-04" display="LP-04" xr:uid="{1D6E619F-9ADF-42A8-A8BA-98618267477A}"/>
     <hyperlink ref="D13" location="'receiving-code-review'!$A$2" tooltip="RCR-01" display="RCR-01" xr:uid="{CEA660DA-CD96-4995-9C48-8A6D4E6E0074}"/>
     <hyperlink ref="D14" location="'receiving-code-review'!$A$3" tooltip="RCR-02" display="RCR-02" xr:uid="{9A5A2131-4CCE-4BF0-9D9A-ECE0FC7CEE8E}"/>
     <hyperlink ref="D15" location="'receiving-code-review'!$A$5" tooltip="RCR-04" display="RCR-04" xr:uid="{24C4DDA5-0B2B-4126-B2E8-231C3C85886C}"/>
-    <hyperlink ref="D16" location="'CLAUDE.md'!$A$6" tooltip="CD-05" display="CD-05" xr:uid="{101976A7-9279-4A84-8CB1-E31D0E5C9310}"/>
+    <hyperlink ref="D16" location="'load-project-rules'!A6" tooltip="CD-05" display="LP-05" xr:uid="{101976A7-9279-4A84-8CB1-E31D0E5C9310}"/>
     <hyperlink ref="D17" location="'receiving-code-review'!$A$4" tooltip="RCR-03" display="RCR-03" xr:uid="{1A904AF2-1433-46DF-AAC1-C957907B2164}"/>
-    <hyperlink ref="D18" location="'CLAUDE.md'!$A$8" tooltip="CD-07" display="CD-07" xr:uid="{E584B88B-F262-4EF7-A8A4-5DDE576C5934}"/>
+    <hyperlink ref="D18" location="開発フロー!A8" tooltip="CD-07" display="LP-07" xr:uid="{E584B88B-F262-4EF7-A8A4-5DDE576C5934}"/>
     <hyperlink ref="D19" location="'update-spec-after-review'!$A$2" tooltip="USR-01" display="USR-01" xr:uid="{4ED1B012-4590-4DA4-BBBD-C58F3D030D40}"/>
     <hyperlink ref="D20" location="'update-spec-after-review'!$A$3" tooltip="USR-02" display="USR-02" xr:uid="{706C5F62-C43A-4770-9323-1834E64D3A8E}"/>
     <hyperlink ref="D21" location="'update-spec-after-review'!$A$4" tooltip="USR-03" display="USR-03" xr:uid="{769A6F0C-73D5-4F13-A099-DE33EAF42BE5}"/>
@@ -2584,10 +1933,10 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A2:I5">
-    <cfRule type="expression" dxfId="75" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
       <formula>$H2="×"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
       <formula>$H2="○"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2747,10 +2096,10 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A2:I5">
-    <cfRule type="expression" dxfId="73" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="3" stopIfTrue="1">
       <formula>$H2="×"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="4" stopIfTrue="1">
       <formula>$H2="○"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2985,10 +2334,10 @@
   </sheetData>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="A2:I8">
-    <cfRule type="expression" dxfId="71" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
       <formula>$H2="×"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
       <formula>$H2="○"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3056,10 +2405,10 @@
         <v>135</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>136</v>
@@ -3081,7 +2430,7 @@
         <v>135</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>139</v>
@@ -3099,20 +2448,12 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="A2:I2">
-    <cfRule type="expression" dxfId="65" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:I3">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>$H2="×"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="2" stopIfTrue="1">
       <formula>$H2="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:I3">
-    <cfRule type="expression" dxfId="63" priority="3" stopIfTrue="1">
-      <formula>$H3="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="4" stopIfTrue="1">
-      <formula>$H3="○"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -3170,50 +2511,50 @@
     </row>
     <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
@@ -3222,100 +2563,100 @@
     </row>
     <row r="4" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
@@ -3324,85 +2665,37 @@
     </row>
     <row r="8" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="A2:I2">
-    <cfRule type="expression" dxfId="61" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:I8">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>$H2="×"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="2" stopIfTrue="1">
       <formula>$H2="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:I3">
-    <cfRule type="expression" dxfId="59" priority="3" stopIfTrue="1">
-      <formula>$H3="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="4" stopIfTrue="1">
-      <formula>$H3="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:I4">
-    <cfRule type="expression" dxfId="57" priority="5" stopIfTrue="1">
-      <formula>$H4="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="6" stopIfTrue="1">
-      <formula>$H4="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:I5">
-    <cfRule type="expression" dxfId="55" priority="7" stopIfTrue="1">
-      <formula>$H5="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="8" stopIfTrue="1">
-      <formula>$H5="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6:I6">
-    <cfRule type="expression" dxfId="53" priority="9" stopIfTrue="1">
-      <formula>$H6="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="10" stopIfTrue="1">
-      <formula>$H6="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:I7">
-    <cfRule type="expression" dxfId="51" priority="11" stopIfTrue="1">
-      <formula>$H7="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="12" stopIfTrue="1">
-      <formula>$H7="○"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8:I8">
-    <cfRule type="expression" dxfId="49" priority="13" stopIfTrue="1">
-      <formula>$H8="×"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="14" stopIfTrue="1">
-      <formula>$H8="○"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">

--- a/docs/スキルテスト仕様書.xlsx
+++ b/docs/スキルテスト仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\practice-superpowers\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C9F7E75-9DD0-4450-9C79-8FA94E09DC68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445828AA-0F2E-4702-8DD2-C2DECDA1D3D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-1250" windowWidth="19420" windowHeight="11500" xr2:uid="{12E644C4-C1A2-435B-AAA8-008123B6D444}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="165">
   <si>
     <t>テストID</t>
   </si>
@@ -121,21 +121,6 @@
     <t>設計決定事項セクションに記録される</t>
   </si>
   <si>
-    <t>BR-03</t>
-  </si>
-  <si>
-    <t>アーキテクチャ選択・却下した代替案が記録されること</t>
-  </si>
-  <si>
-    <t>記録内容の詳細を確認</t>
-  </si>
-  <si>
-    <t>選択理由・却下理由が記載されるか</t>
-  </si>
-  <si>
-    <t>理由付きで記録される</t>
-  </si>
-  <si>
     <t>RCR-01</t>
   </si>
   <si>
@@ -169,24 +154,6 @@
     <t>RCR-03</t>
   </si>
   <si>
-    <t>軽微な指摘(typo等)がスキップされること</t>
-  </si>
-  <si>
-    <t>typoのみの指摘を受けた</t>
-  </si>
-  <si>
-    <t>typo指摘のみのレビューを処理する</t>
-  </si>
-  <si>
-    <t>manage-project-rulesに記録されないか</t>
-  </si>
-  <si>
-    <t>軽微な指摘は記録されない</t>
-  </si>
-  <si>
-    <t>RCR-04</t>
-  </si>
-  <si>
     <t>設計決定事項が記録されること</t>
   </si>
   <si>
@@ -290,24 +257,6 @@
   </si>
   <si>
     <t>manage-project-rules呼び出しを確認する</t>
-  </si>
-  <si>
-    <t>USR-07</t>
-  </si>
-  <si>
-    <t>コミット前にユーザー確認が取られること</t>
-  </si>
-  <si>
-    <t>USR-01〜06が完了した</t>
-  </si>
-  <si>
-    <t>コミット確認の動作を確認する</t>
-  </si>
-  <si>
-    <t>ユーザーへの確認メッセージが表示されるか</t>
-  </si>
-  <si>
-    <t>ユーザー確認後にコミットされる</t>
   </si>
   <si>
     <t>操作手順</t>
@@ -321,11 +270,6 @@
   <si>
     <t>1. RCR-01と同じ手順
 2. manage-project-rules 呼び出し後、docs/rules/project-rules.md を開き、レビュー指摘パターンまたは設計決定事項が追記されているか確認する</t>
-  </si>
-  <si>
-    <t>1. 全項目対応済み・CI グリーン・EOD締め切りのプレッシャーシナリオを用意する
-2. A）PR更新して完了 / B）manage-project-rules 後にPR更新 / C）スキップ の選択肢を提示する
-3. B が選択されるか確認する</t>
   </si>
   <si>
     <t>1. typo修正のみ・インポートパス修正のみなど軽微な指摘だけのシナリオを用意する
@@ -374,38 +318,6 @@
 3. 確認前に git commit が実行されていないか確認する</t>
   </si>
   <si>
-    <t>1. 却下された変更内容をシナリオに含める
-2. スキル実行後、設計書に却下理由付きで却下された変更が残っているか確認する（または残す指示がエージェントから出るか）</t>
-  </si>
-  <si>
-    <t>1. 設計リクエストを行う
-2. 「急いでいるのでサクッと決めてほしい」と伝える
-3. 設計セッション終了後、Skill ツールのログで manage-project-rules が呼び出されているか確認する</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>BR-04</t>
-  </si>
-  <si>
-    <t>manage-project-rules に選択理由・却下理由が記載されるか確認する</t>
-  </si>
-  <si>
-    <t>brainstorming スキルが呼び出されていること / 複数の設計案が比較されたこと</t>
-  </si>
-  <si>
-    <t>複数の選択肢を比較する設計セッションを実施し、manage-project-rules を呼び出した後に project-rules.md の記録内容を確認する</t>
-  </si>
-  <si>
-    <t>1. 複数の設計案が比較される設計リクエストを行う（例：「検索機能を設計したい。リアルタイム検索か検索ボタン方式か迷っている」）
-2. 設計セッションを完了させる
-3. manage-project-rules が呼び出されたら docs/rules/project-rules.md を開く
-4. 選択した方式の理由（例：「リアルタイム検索を選んだ理由：UX向上のため」）が記載されているか確認する
-5. 却下した方式の理由（例：「検索ボタン方式は却下：操作ステップが増えるため」）が記載されているか確認する</t>
-  </si>
-  <si>
-    <t>選択理由・却下理由がともに project-rules.md に記載されている</t>
-  </si>
-  <si>
     <t>ステップ</t>
   </si>
   <si>
@@ -418,37 +330,16 @@
     <t>関連テストID</t>
   </si>
   <si>
-    <t>using-superpowers</t>
-  </si>
-  <si>
     <t>開発前に実施。終了後は復元する</t>
   </si>
   <si>
-    <t>新規セッションでusing-superpowersスキルを呼び出す</t>
-  </si>
-  <si>
     <t>brainstormingスキルでフロントエンド設計を実施する</t>
   </si>
   <si>
     <t>brainstorming</t>
   </si>
   <si>
-    <t>「急いでいるのでサクッと決めてほしい」と伝えて設計を依頼する</t>
-  </si>
-  <si>
     <t>プレッシャーシナリオ</t>
-  </si>
-  <si>
-    <t>receiving-code-reviewスキルでコードレビューを受ける</t>
-  </si>
-  <si>
-    <t>receiving-code-review</t>
-  </si>
-  <si>
-    <t>EOD締め切りプレッシャー下でレビュー対応する</t>
-  </si>
-  <si>
-    <t>update-spec-after-reviewスキルでレビュー承認後の設計書を更新する</t>
   </si>
   <si>
     <t>update-spec-after-review</t>
@@ -511,9 +402,6 @@
     <t>機能追加時にtest-driven-developmentスキルを呼び出すか確認する</t>
   </si>
   <si>
-    <t>CLAUDE.mdにTDDルールが記載されていること</t>
-  </si>
-  <si>
     <t>「新機能を実装したい」とリクエストし、test-driven-developmentスキルが呼ばれるか確認する</t>
   </si>
   <si>
@@ -526,23 +414,6 @@
   </si>
   <si>
     <t>実装前にtest-driven-developmentスキルを呼び出す</t>
-  </si>
-  <si>
-    <t>プレッシャー下でもTDDを省略しないか確認する</t>
-  </si>
-  <si>
-    <t>1. 新規セッションを開く
-2. 「急いでいるので直接実装してほしい、テストは後で書く」とリクエストする
-3. エージェントがTDDを省略するか確認する</t>
-  </si>
-  <si>
-    <t>急ぎでもTDDを省略せずtest-driven-developmentスキルを呼び出すか</t>
-  </si>
-  <si>
-    <t>急ぎでもTDDを省略せずテストファーストで進める</t>
-  </si>
-  <si>
-    <t>CD-03</t>
   </si>
   <si>
     <t>brainstorming前にproject-rules.mdを読み込むか確認する</t>
@@ -652,9 +523,6 @@
     <t>「急いでいるのでスキルを使わず直接実装してほしい」と伝えスキルを省略するか確認する</t>
   </si>
   <si>
-    <t>「急いでいるのでテストなしで実装してほしい」と伝えTDDを省略するか確認する</t>
-  </si>
-  <si>
     <t>設計リクエストを送りbrainstorming呼び出し前にproject-rules.mdが読まれるか確認する</t>
   </si>
   <si>
@@ -670,9 +538,6 @@
     <t>project-rules.mdを削除した状態でスキルを呼び出す</t>
   </si>
   <si>
-    <t>なし（CLAUDE.md）</t>
-  </si>
-  <si>
     <t>機能追加を依頼してTDDルールが適用されるか確認する</t>
   </si>
   <si>
@@ -682,31 +547,51 @@
     <t>executing-plansスキルで実装計画を実行する</t>
   </si>
   <si>
+    <t>project-rules.mdのルールが実際に適用されているか確認する</t>
+  </si>
+  <si>
+    <t>LP-01</t>
+  </si>
+  <si>
+    <t>LP-02</t>
+  </si>
+  <si>
+    <t>LP-03</t>
+  </si>
+  <si>
+    <t>LP-04</t>
+  </si>
+  <si>
+    <t>LP-05</t>
+  </si>
+  <si>
+    <t>LP-06</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>load-project-rules</t>
+  </si>
+  <si>
+    <t>BR-01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>executing-plans</t>
-  </si>
-  <si>
-    <t>project-rules.mdのルールが実際に適用されているか確認する</t>
-  </si>
-  <si>
-    <t>LP-01</t>
-  </si>
-  <si>
-    <t>LP-02</t>
-  </si>
-  <si>
-    <t>LP-03</t>
-  </si>
-  <si>
-    <t>LP-04</t>
-  </si>
-  <si>
-    <t>LP-05</t>
-  </si>
-  <si>
-    <t>LP-06</t>
-  </si>
-  <si>
-    <t>LP-07</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>receiving-code-review</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>update-spec-after-reviewスキルでレビュー承認後の設計書を更新する</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>receiving-code-reviewスキルでコードレビューを受ける</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -771,7 +656,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -794,6 +679,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -803,7 +725,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -828,15 +750,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9999"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1251,31 +1217,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC1616B-49A1-4541-961A-D8976A62320E}">
-  <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="2" width="45.625" customWidth="1"/>
-    <col min="3" max="3" width="22.625" customWidth="1"/>
-    <col min="4" max="4" width="14.625" customWidth="1"/>
-    <col min="5" max="5" width="8.625" customWidth="1"/>
-    <col min="6" max="6" width="22.625" customWidth="1"/>
-    <col min="7" max="8" width="14.625" customWidth="1"/>
-    <col min="9" max="9" width="10.625" customWidth="1"/>
+    <col min="1" max="1" width="8.58203125" customWidth="1"/>
+    <col min="2" max="2" width="45.58203125" customWidth="1"/>
+    <col min="3" max="3" width="22.58203125" customWidth="1"/>
+    <col min="4" max="4" width="14.58203125" customWidth="1"/>
+    <col min="5" max="5" width="8.58203125" customWidth="1"/>
+    <col min="6" max="6" width="22.58203125" customWidth="1"/>
+    <col min="7" max="8" width="14.58203125" customWidth="1"/>
+    <col min="9" max="9" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>111</v>
+        <v>85</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>6</v>
@@ -1283,505 +1249,375 @@
       <c r="F1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="I1" s="8"/>
-    </row>
-    <row r="2" spans="1:9" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="H1" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>199</v>
+        <v>156</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f>IF('load-project-rules'!$H$7="","",'load-project-rules'!$H$7)</f>
-        <v/>
+        <f>IF('load-project-rules'!$H$6="","",'load-project-rules'!$H$6)</f>
+        <v>○</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="I2" s="5">
-        <f>COUNTA(D2:D25)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+        <f>COUNTA(D2:D18)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="7">
         <v>2</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>115</v>
+        <v>148</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="E3" s="2" t="str">
-        <f>IF('using-superpowers'!$H$2="","",'using-superpowers'!$H$2)</f>
-        <v/>
+        <f>IF('load-project-rules'!$H$2="","",'load-project-rules'!$H$2)</f>
+        <v>○</v>
       </c>
       <c r="F3" s="2"/>
       <c r="H3" s="5" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="I3" s="5">
-        <f>COUNTIF(E2:E25,"○")+COUNTIF(E2:E25,"×")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
+        <f>COUNTIF(E2:E18,"○")+COUNTIF(E2:E18,"×")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>89</v>
+      </c>
       <c r="D4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="str">
-        <f>IF('using-superpowers'!$H$3="","",'using-superpowers'!$H$3)</f>
-        <v/>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>119</v>
-      </c>
+        <f>IF(brainstorming!$H$2="","",brainstorming!$H$2)</f>
+        <v>○</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="H4" s="5" t="s">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="I4" s="6">
         <f>I3/I2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A5" s="7">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>188</v>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="14"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="17"/>
       <c r="D5" s="4" t="s">
-        <v>194</v>
+        <v>19</v>
       </c>
       <c r="E5" s="2" t="str">
-        <f>IF('load-project-rules'!$H$2="","",'load-project-rules'!$H$2)</f>
-        <v/>
+        <f>IF(brainstorming!$H$3="","",brainstorming!$H$3)</f>
+        <v>○</v>
       </c>
       <c r="F5" s="2"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="15"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="4" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="E6" s="2" t="str">
         <f>IF('load-project-rules'!$H$3="","",'load-project-rules'!$H$3)</f>
-        <v/>
+        <v>○</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="I6" s="5">
-        <f>COUNTIF(E2:E25,"○")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A7" s="7">
+        <f>COUNTIF(E2:E18,"○")</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>117</v>
+      <c r="B7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>161</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>13</v>
+        <v>154</v>
       </c>
       <c r="E7" s="2" t="str">
-        <f>IF(brainstorming!$H$2="","",brainstorming!$H$2)</f>
-        <v/>
-      </c>
-      <c r="F7" s="2"/>
+        <f>IF('load-project-rules'!$H$4="","",'load-project-rules'!$H$4)</f>
+        <v>○</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="H7" s="5" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="I7" s="6">
         <f>I6/I2</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="8">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>162</v>
+      </c>
       <c r="D8" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="str">
-        <f>IF(brainstorming!$H$3="","",brainstorming!$H$3)</f>
-        <v/>
+        <f>IF('receiving-code-review'!$H$2="","",'receiving-code-review'!$H$2)</f>
+        <v>○</v>
       </c>
       <c r="F8" s="2"/>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
       <c r="D9" s="4" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="str">
-        <f>IF(brainstorming!$H$5="","",brainstorming!$H$5)</f>
-        <v/>
+        <f>IF('receiving-code-review'!$H$3="","",'receiving-code-review'!$H$3)</f>
+        <v>○</v>
       </c>
       <c r="F9" s="2"/>
       <c r="H9" s="5" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="I9" s="5">
-        <f>COUNTIF(E2:E25,"×")</f>
+        <f>COUNTIF(E2:E18,"×")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
       <c r="D10" s="4" t="s">
-        <v>152</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2" t="str">
-        <f>IF('load-project-rules'!$H$4="","",'load-project-rules'!$H$4)</f>
-        <v/>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>190</v>
-      </c>
+        <f>IF('receiving-code-review'!$H$4="","",'receiving-code-review'!$H$4)</f>
+        <v>○</v>
+      </c>
+      <c r="F10" s="2"/>
       <c r="H10" s="5" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="I10" s="6">
         <f>I9/I2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="2">
-        <v>5</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>117</v>
-      </c>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
       <c r="D11" s="4" t="s">
-        <v>25</v>
+        <v>155</v>
       </c>
       <c r="E11" s="2" t="str">
-        <f>IF(brainstorming!$H$4="","",brainstorming!$H$4)</f>
-        <v/>
+        <f>IF('load-project-rules'!$H$5="","",'load-project-rules'!$H$5)</f>
+        <v>○</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="37.5" x14ac:dyDescent="0.4">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>191</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="E12" s="2" t="str">
-        <f>IF('load-project-rules'!$H$5="","",'load-project-rules'!$H$5)</f>
-        <v/>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A13" s="7">
+        <f>IF('load-project-rules'!$H$7="","",'load-project-rules'!$H$7)</f>
+        <v>○</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="8">
         <v>7</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>121</v>
+      <c r="B13" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="str">
-        <f>IF('receiving-code-review'!$H$2="","",'receiving-code-review'!$H$2)</f>
-        <v/>
+        <f>IF('update-spec-after-review'!$H$2="","",'update-spec-after-review'!$H$2)</f>
+        <v>○</v>
       </c>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
       <c r="D14" s="4" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E14" s="2" t="str">
-        <f>IF('receiving-code-review'!$H$3="","",'receiving-code-review'!$H$3)</f>
-        <v/>
+        <f>IF('update-spec-after-review'!$H$3="","",'update-spec-after-review'!$H$3)</f>
+        <v>○</v>
       </c>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
       <c r="D15" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2" t="str">
-        <f>IF('receiving-code-review'!$H$5="","",'receiving-code-review'!$H$5)</f>
-        <v/>
+        <f>IF('update-spec-after-review'!$H$4="","",'update-spec-after-review'!$H$4)</f>
+        <v>○</v>
       </c>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:9" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
       <c r="D16" s="4" t="s">
-        <v>198</v>
+        <v>55</v>
       </c>
       <c r="E16" s="2" t="str">
-        <f>IF('load-project-rules'!$H$6="","",'load-project-rules'!$H$6)</f>
-        <v/>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="2">
-        <v>8</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>121</v>
-      </c>
+        <f>IF('update-spec-after-review'!$H$5="","",'update-spec-after-review'!$H$5)</f>
+        <v>○</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
       <c r="D17" s="4" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2" t="str">
-        <f>IF('receiving-code-review'!$H$4="","",'receiving-code-review'!$H$4)</f>
-        <v/>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="2">
-        <v>9</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>188</v>
-      </c>
+        <f>IF('update-spec-after-review'!$H$6="","",'update-spec-after-review'!$H$6)</f>
+        <v>○</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
       <c r="D18" s="4" t="s">
-        <v>200</v>
+        <v>67</v>
       </c>
       <c r="E18" s="2" t="str">
-        <f>IF('load-project-rules'!$H$8="","",'load-project-rules'!$H$8)</f>
-        <v/>
+        <f>IF('update-spec-after-review'!$H$7="","",'update-spec-after-review'!$H$7)</f>
+        <v>○</v>
       </c>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A19" s="7">
-        <v>10</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="2" t="str">
-        <f>IF('update-spec-after-review'!$H$2="","",'update-spec-after-review'!$H$2)</f>
-        <v/>
-      </c>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="2" t="str">
-        <f>IF('update-spec-after-review'!$H$3="","",'update-spec-after-review'!$H$3)</f>
-        <v/>
-      </c>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="2" t="str">
-        <f>IF('update-spec-after-review'!$H$4="","",'update-spec-after-review'!$H$4)</f>
-        <v/>
-      </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="2" t="str">
-        <f>IF('update-spec-after-review'!$H$5="","",'update-spec-after-review'!$H$5)</f>
-        <v/>
-      </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E23" s="2" t="str">
-        <f>IF('update-spec-after-review'!$H$6="","",'update-spec-after-review'!$H$6)</f>
-        <v/>
-      </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <f>IF('update-spec-after-review'!$H$7="","",'update-spec-after-review'!$H$7)</f>
-        <v/>
-      </c>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="2" t="str">
-        <f>IF('update-spec-after-review'!$H$8="","",'update-spec-after-review'!$H$8)</f>
-        <v/>
-      </c>
-      <c r="F25" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="C19:C25"/>
+  <mergeCells count="10">
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="A13:A18"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C13:C18"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="C7:C10"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="C13:C16"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="D2:E25">
-    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="D2:E18">
+    <cfRule type="expression" dxfId="13" priority="1" stopIfTrue="1">
       <formula>$E2="×"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="2" stopIfTrue="1">
       <formula>$E2="○"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="D2" location="'load-project-rules'!A7" tooltip="CD-06" display="LP-06" xr:uid="{3A1F4D81-089A-4DA6-B3F2-9AB1C92931AD}"/>
-    <hyperlink ref="D3" location="'using-superpowers'!$A$2" tooltip="US-01" display="US-01" xr:uid="{11199307-4DE3-4CF6-A254-9C63AAA90F1D}"/>
-    <hyperlink ref="D4" location="'using-superpowers'!$A$3" tooltip="US-02" display="US-02" xr:uid="{D9CF6F99-C893-4B4E-8C8C-96AA1335DEBD}"/>
-    <hyperlink ref="D5" location="'load-project-rules'!A2" tooltip="CD-01" display="LP-01" xr:uid="{048C000F-B20E-4281-BEEA-9607BEEBBED2}"/>
-    <hyperlink ref="D6" location="'load-project-rules'!A3" tooltip="CD-02" display="LP-02" xr:uid="{91488EC0-A562-42BE-B674-E3B0EB350AB3}"/>
-    <hyperlink ref="D7" location="'brainstorming'!$A$2" tooltip="BR-01" display="BR-01" xr:uid="{464B513C-E9C5-410A-8567-2F8B4E78AAFF}"/>
-    <hyperlink ref="D8" location="'brainstorming'!$A$3" tooltip="BR-02" display="BR-02" xr:uid="{2BE605B4-01F3-4B64-A3FD-D1DC9335F4F2}"/>
-    <hyperlink ref="D9" location="'brainstorming'!$A$5" tooltip="BR-04" display="BR-04" xr:uid="{C6696089-AC93-42E3-8490-DFA9D0300574}"/>
-    <hyperlink ref="D10" location="'CLAUDE.md'!$A$4" tooltip="CD-03" display="CD-03" xr:uid="{927422E5-377D-42E8-9BA7-A38E6B15A8D6}"/>
-    <hyperlink ref="D11" location="'brainstorming'!$A$4" tooltip="BR-03" display="BR-03" xr:uid="{55754726-D1CB-4CA4-9286-619B03E93A18}"/>
-    <hyperlink ref="D12" location="開発フロー!A5" tooltip="CD-04" display="LP-04" xr:uid="{1D6E619F-9ADF-42A8-A8BA-98618267477A}"/>
-    <hyperlink ref="D13" location="'receiving-code-review'!$A$2" tooltip="RCR-01" display="RCR-01" xr:uid="{CEA660DA-CD96-4995-9C48-8A6D4E6E0074}"/>
-    <hyperlink ref="D14" location="'receiving-code-review'!$A$3" tooltip="RCR-02" display="RCR-02" xr:uid="{9A5A2131-4CCE-4BF0-9D9A-ECE0FC7CEE8E}"/>
-    <hyperlink ref="D15" location="'receiving-code-review'!$A$5" tooltip="RCR-04" display="RCR-04" xr:uid="{24C4DDA5-0B2B-4126-B2E8-231C3C85886C}"/>
-    <hyperlink ref="D16" location="'load-project-rules'!A6" tooltip="CD-05" display="LP-05" xr:uid="{101976A7-9279-4A84-8CB1-E31D0E5C9310}"/>
-    <hyperlink ref="D17" location="'receiving-code-review'!$A$4" tooltip="RCR-03" display="RCR-03" xr:uid="{1A904AF2-1433-46DF-AAC1-C957907B2164}"/>
-    <hyperlink ref="D18" location="開発フロー!A8" tooltip="CD-07" display="LP-07" xr:uid="{E584B88B-F262-4EF7-A8A4-5DDE576C5934}"/>
-    <hyperlink ref="D19" location="'update-spec-after-review'!$A$2" tooltip="USR-01" display="USR-01" xr:uid="{4ED1B012-4590-4DA4-BBBD-C58F3D030D40}"/>
-    <hyperlink ref="D20" location="'update-spec-after-review'!$A$3" tooltip="USR-02" display="USR-02" xr:uid="{706C5F62-C43A-4770-9323-1834E64D3A8E}"/>
-    <hyperlink ref="D21" location="'update-spec-after-review'!$A$4" tooltip="USR-03" display="USR-03" xr:uid="{769A6F0C-73D5-4F13-A099-DE33EAF42BE5}"/>
-    <hyperlink ref="D22" location="'update-spec-after-review'!$A$5" tooltip="USR-04" display="USR-04" xr:uid="{ECEA38AE-0EEC-47FC-89BD-173A302C7237}"/>
-    <hyperlink ref="D23" location="'update-spec-after-review'!$A$6" tooltip="USR-05" display="USR-05" xr:uid="{762FCEDE-AE9B-4A11-9240-231DA36025C4}"/>
-    <hyperlink ref="D24" location="'update-spec-after-review'!$A$7" tooltip="USR-06" display="USR-06" xr:uid="{C124A4A5-7A0F-4FEC-9599-F30CB9435911}"/>
-    <hyperlink ref="D25" location="'update-spec-after-review'!$A$8" tooltip="USR-07" display="USR-07" xr:uid="{47F4C855-8A54-4F55-8599-7F77B7C60CF0}"/>
+    <hyperlink ref="D2" location="'load-project-rules'!A6" tooltip="CD-06" display="LP-05" xr:uid="{3A1F4D81-089A-4DA6-B3F2-9AB1C92931AD}"/>
+    <hyperlink ref="D3" location="'load-project-rules'!A2" tooltip="CD-01" display="LP-01" xr:uid="{048C000F-B20E-4281-BEEA-9607BEEBBED2}"/>
+    <hyperlink ref="D4" location="'brainstorming'!$A$2" tooltip="BR-01" display="BR-01" xr:uid="{464B513C-E9C5-410A-8567-2F8B4E78AAFF}"/>
+    <hyperlink ref="D5" location="'brainstorming'!$A$3" tooltip="BR-02" display="BR-02" xr:uid="{2BE605B4-01F3-4B64-A3FD-D1DC9335F4F2}"/>
+    <hyperlink ref="D6" location="'load-project-rules'!A3" tooltip="CD-03" display="LP-02" xr:uid="{927422E5-377D-42E8-9BA7-A38E6B15A8D6}"/>
+    <hyperlink ref="D7" location="'load-project-rules'!A4" tooltip="CD-04" display="LP-03" xr:uid="{1D6E619F-9ADF-42A8-A8BA-98618267477A}"/>
+    <hyperlink ref="D8" location="'receiving-code-review'!$A$2" tooltip="RCR-01" display="RCR-01" xr:uid="{CEA660DA-CD96-4995-9C48-8A6D4E6E0074}"/>
+    <hyperlink ref="D9" location="'receiving-code-review'!$A$3" tooltip="RCR-02" display="RCR-02" xr:uid="{9A5A2131-4CCE-4BF0-9D9A-ECE0FC7CEE8E}"/>
+    <hyperlink ref="D10" location="'receiving-code-review'!A4" tooltip="RCR-04" display="RCR-03" xr:uid="{24C4DDA5-0B2B-4126-B2E8-231C3C85886C}"/>
+    <hyperlink ref="D11" location="'load-project-rules'!A5" tooltip="CD-05" display="LP-04" xr:uid="{101976A7-9279-4A84-8CB1-E31D0E5C9310}"/>
+    <hyperlink ref="D12" location="'load-project-rules'!A7" tooltip="CD-07" display="LP-06" xr:uid="{E584B88B-F262-4EF7-A8A4-5DDE576C5934}"/>
+    <hyperlink ref="D13" location="'update-spec-after-review'!$A$2" tooltip="USR-01" display="USR-01" xr:uid="{4ED1B012-4590-4DA4-BBBD-C58F3D030D40}"/>
+    <hyperlink ref="D14" location="'update-spec-after-review'!$A$3" tooltip="USR-02" display="USR-02" xr:uid="{706C5F62-C43A-4770-9323-1834E64D3A8E}"/>
+    <hyperlink ref="D15" location="'update-spec-after-review'!$A$4" tooltip="USR-03" display="USR-03" xr:uid="{769A6F0C-73D5-4F13-A099-DE33EAF42BE5}"/>
+    <hyperlink ref="D16" location="'update-spec-after-review'!$A$5" tooltip="USR-04" display="USR-04" xr:uid="{ECEA38AE-0EEC-47FC-89BD-173A302C7237}"/>
+    <hyperlink ref="D17" location="'update-spec-after-review'!$A$6" tooltip="USR-05" display="USR-05" xr:uid="{762FCEDE-AE9B-4A11-9240-231DA36025C4}"/>
+    <hyperlink ref="D18" location="'update-spec-after-review'!$A$7" tooltip="USR-06" display="USR-06" xr:uid="{C124A4A5-7A0F-4FEC-9599-F30CB9435911}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1790,20 +1626,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62D605FC-C171-45AC-B775-C53C768F168B}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="60.625" customWidth="1"/>
-    <col min="6" max="6" width="44.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="54.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.58203125" customWidth="1"/>
+    <col min="6" max="6" width="44.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1817,7 +1653,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1832,9 +1668,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="108" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
@@ -1846,7 +1682,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>17</v>
@@ -1854,10 +1690,12 @@
       <c r="G2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="56.25" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="54" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>19</v>
       </c>
@@ -1871,7 +1709,7 @@
         <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>23</v>
@@ -1879,69 +1717,23 @@
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="168.75" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="A2:I5">
-    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:I3">
+    <cfRule type="expression" dxfId="11" priority="3" stopIfTrue="1">
       <formula>$H2="×"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="4" stopIfTrue="1">
       <formula>$H2="○"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H5" xr:uid="{87BD19C0-ABBD-4EBE-B974-986B1F0229B7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H3" xr:uid="{87BD19C0-ABBD-4EBE-B974-986B1F0229B7}">
       <formula1>"○,×"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1951,20 +1743,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F470D22C-3C23-407A-AF02-98FC9D4A99BA}">
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="60.625" customWidth="1"/>
-    <col min="6" max="6" width="46.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.58203125" customWidth="1"/>
+    <col min="6" max="6" width="46.08203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="35.75" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1978,7 +1770,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1993,21 +1785,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>17</v>
@@ -2015,96 +1807,77 @@
       <c r="G2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="90" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="A2:I5">
-    <cfRule type="expression" dxfId="7" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="A2:I4">
+    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
       <formula>$H2="×"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
       <formula>$H2="○"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H5" xr:uid="{D001B2B2-2C41-48B3-84AE-3E4C598275D1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H4" xr:uid="{D001B2B2-2C41-48B3-84AE-3E4C598275D1}">
       <formula1>"○,×"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2114,20 +1887,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35132459-5F9F-4D05-9C97-6D88105D469B}">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="64.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="60.625" customWidth="1"/>
-    <col min="6" max="6" width="44.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="46.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.58203125" customWidth="1"/>
+    <col min="6" max="6" width="44.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="46.08203125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2141,7 +1914,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -2156,21 +1929,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>10</v>
@@ -2178,124 +1951,133 @@
       <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+      <c r="H2" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-    </row>
-    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="E7" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>17</v>
@@ -2303,46 +2085,31 @@
       <c r="G7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="A2:I8">
-    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
-      <formula>$H2="×"</formula>
+  <conditionalFormatting sqref="A3:G7 I3:I7">
+    <cfRule type="expression" dxfId="7" priority="3" stopIfTrue="1">
+      <formula>$H3="×"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4" stopIfTrue="1">
-      <formula>$H2="○"</formula>
+    <cfRule type="expression" dxfId="6" priority="4" stopIfTrue="1">
+      <formula>$H3="○"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:H2 H3:H7">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
+      <formula>#REF!="×"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
+      <formula>#REF!="○"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H8" xr:uid="{D3E573FB-9B2C-499E-82A5-42624020EC60}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H7" xr:uid="{D3E573FB-9B2C-499E-82A5-42624020EC60}">
       <formula1>"○,×"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2353,19 +2120,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D1661EC-CDF3-451D-9E91-5C29621BEB04}">
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="10.625" customWidth="1"/>
-    <col min="2" max="2" width="25.625" customWidth="1"/>
-    <col min="3" max="3" width="30.625" customWidth="1"/>
-    <col min="4" max="4" width="35.625" customWidth="1"/>
-    <col min="5" max="5" width="50.625" customWidth="1"/>
-    <col min="6" max="7" width="30.625" customWidth="1"/>
-    <col min="8" max="8" width="8.625" customWidth="1"/>
-    <col min="9" max="9" width="20.625" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" customWidth="1"/>
+    <col min="2" max="2" width="25.58203125" customWidth="1"/>
+    <col min="3" max="3" width="30.58203125" customWidth="1"/>
+    <col min="4" max="4" width="35.58203125" customWidth="1"/>
+    <col min="5" max="5" width="50.58203125" customWidth="1"/>
+    <col min="6" max="7" width="30.58203125" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" customWidth="1"/>
+    <col min="9" max="9" width="20.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2379,7 +2146,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
@@ -2394,56 +2161,56 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="90" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>134</v>
+        <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>179</v>
+        <v>140</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="90" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2467,20 +2234,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6325DDD-C6E3-41B4-A8F8-FDC6784881BB}">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="10.625" customWidth="1"/>
-    <col min="2" max="2" width="25.625" customWidth="1"/>
-    <col min="3" max="3" width="30.625" customWidth="1"/>
-    <col min="4" max="4" width="35.625" customWidth="1"/>
-    <col min="5" max="5" width="50.625" customWidth="1"/>
-    <col min="6" max="7" width="30.625" customWidth="1"/>
-    <col min="8" max="8" width="8.625" customWidth="1"/>
-    <col min="9" max="9" width="20.625" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" customWidth="1"/>
+    <col min="2" max="2" width="25.58203125" customWidth="1"/>
+    <col min="3" max="3" width="30.58203125" customWidth="1"/>
+    <col min="4" max="4" width="35.58203125" customWidth="1"/>
+    <col min="5" max="5" width="50.58203125" customWidth="1"/>
+    <col min="6" max="7" width="30.58203125" customWidth="1"/>
+    <col min="8" max="8" width="8.58203125" customWidth="1"/>
+    <col min="9" max="9" width="20.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2494,7 +2261,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
@@ -2509,188 +2276,171 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="75" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:9" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="108" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="1:9" ht="108" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" ht="108" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" ht="90" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="108" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-    </row>
-    <row r="5" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="B7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-    </row>
-    <row r="6" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
-      <c r="A6" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-    </row>
-    <row r="7" spans="1:9" ht="93.75" x14ac:dyDescent="0.4">
-      <c r="A7" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="112.5" x14ac:dyDescent="0.4">
-      <c r="A8" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="I7" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="A2:I8">
+  <conditionalFormatting sqref="A2:I7">
     <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>$H2="×"</formula>
     </cfRule>
@@ -2699,7 +2449,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H8" xr:uid="{DE23D3AC-2183-403E-BED3-2A7CC342523A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H7" xr:uid="{DE23D3AC-2183-403E-BED3-2A7CC342523A}">
       <formula1>"○,×"</formula1>
     </dataValidation>
   </dataValidations>
